--- a/キックスターター/ホラーゲーム系クラウドファンディングプロジェクト一覧.xlsx
+++ b/キックスターター/ホラーゲーム系クラウドファンディングプロジェクト一覧.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\OneDrive\ドキュメント\training\キックスターター\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{16EB2848-8793-42C6-B9D1-C7A0E9A281DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BCE33D3-79D0-41A1-8526-C2FA44428226}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A4A5CA34-1A67-4CB3-8444-3967CF4417ED}"/>
   </bookViews>
@@ -56,50 +56,55 @@
     <t>日本のホラーゲーム。総プレッジ額400万円以上を達成</t>
   </si>
   <si>
+    <t>The Sinking City 2</t>
+  </si>
+  <si>
+    <t>『バイオハザード』のような雰囲気を持つホラーゲーム</t>
+  </si>
+  <si>
+    <t>Hide Or Die - Large Scale Asymmetrical Horror</t>
+  </si>
+  <si>
+    <t>探索要素のある非対称型ホラーゲーム</t>
+  </si>
+  <si>
+    <t>Last Year - 5 vs 1 Multiplayer Survival Horror</t>
+  </si>
+  <si>
+    <t>5人が協力して1人の犯人から逃げるマルチプレイ型ホラーゲーム</t>
+  </si>
+  <si>
+    <t>Visage — Psychological horror game</t>
+  </si>
+  <si>
+    <t>家の中を探索するサイコロジカルホラーゲーム</t>
+  </si>
+  <si>
     <t>https://www.kickstarter.com/projects/kazumigamesstudios/walk-horror-game?ref=discover_saved_projects&amp;category_id=35</t>
-  </si>
-  <si>
-    <t>The Sinking City 2</t>
-  </si>
-  <si>
-    <t>『バイオハザード』のような雰囲気を持つホラーゲーム</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://www.kickstarter.com/projects/frogwares/the-sinking-city-2?ref=discover_saved_projects&amp;category_id=35</t>
-  </si>
-  <si>
-    <t>Hide Or Die - Large Scale Asymmetrical Horror</t>
-  </si>
-  <si>
-    <t>探索要素のある非対称型ホラーゲーム</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://www.kickstarter.com/projects/hideordie/hide-or-die-asymmetrical-horror-royale?ref=discover_saved_projects&amp;category_id=35</t>
-  </si>
-  <si>
-    <t>Last Year - 5 vs 1 Multiplayer Survival Horror</t>
-  </si>
-  <si>
-    <t>5人が協力して1人の犯人から逃げるマルチプレイ型ホラーゲーム</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://www.kickstarter.com/projects/lastyear/last-year-5-vs-1-multiplayer-survival-horror?ref=discover_saved_projects&amp;category_id=35</t>
-  </si>
-  <si>
-    <t>Visage — Psychological horror game</t>
-  </si>
-  <si>
-    <t>家の中を探索するサイコロジカルホラーゲーム</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://www.kickstarter.com/projects/1058493022/visage-horror-game?ref=discover_saved_projects&amp;category_id=35</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -110,6 +115,15 @@
     </font>
     <font>
       <sz val="6"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="游ゴシック"/>
       <family val="2"/>
       <charset val="128"/>
@@ -163,23 +177,30 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -537,57 +558,64 @@
       <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>5</v>
+      <c r="C2" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="73.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>8</v>
+      <c r="C3" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="91.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="91.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="73.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{8E38AAE7-D099-4154-90F0-AB8860FC670E}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{647C6DA6-4500-44D5-B1DD-3AE54134BD9A}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{A907E482-843B-4A4A-8C17-4775DABD82FF}"/>
+    <hyperlink ref="C5" r:id="rId4" xr:uid="{6F5D9F3F-70FE-445F-9C2E-3C45F4D3DB65}"/>
+    <hyperlink ref="C6" r:id="rId5" xr:uid="{47EC2053-A8D4-4629-ADA4-C36C704398C2}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/キックスターター/ホラーゲーム系クラウドファンディングプロジェクト一覧.xlsx
+++ b/キックスターター/ホラーゲーム系クラウドファンディングプロジェクト一覧.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\OneDrive\ドキュメント\training\キックスターター\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BCE33D3-79D0-41A1-8526-C2FA44428226}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB47C1B6-CE06-4591-97C7-D6B0286F5C20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A4A5CA34-1A67-4CB3-8444-3967CF4417ED}"/>
   </bookViews>
@@ -59,27 +59,15 @@
     <t>The Sinking City 2</t>
   </si>
   <si>
-    <t>『バイオハザード』のような雰囲気を持つホラーゲーム</t>
-  </si>
-  <si>
     <t>Hide Or Die - Large Scale Asymmetrical Horror</t>
   </si>
   <si>
-    <t>探索要素のある非対称型ホラーゲーム</t>
-  </si>
-  <si>
     <t>Last Year - 5 vs 1 Multiplayer Survival Horror</t>
   </si>
   <si>
-    <t>5人が協力して1人の犯人から逃げるマルチプレイ型ホラーゲーム</t>
-  </si>
-  <si>
     <t>Visage — Psychological horror game</t>
   </si>
   <si>
-    <t>家の中を探索するサイコロジカルホラーゲーム</t>
-  </si>
-  <si>
     <t>https://www.kickstarter.com/projects/kazumigamesstudios/walk-horror-game?ref=discover_saved_projects&amp;category_id=35</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -97,6 +85,22 @@
   </si>
   <si>
     <t>https://www.kickstarter.com/projects/1058493022/visage-horror-game?ref=discover_saved_projects&amp;category_id=35</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>『バイオハザード』のようなホラーゲーム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>探索ホラーゲーム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>５名のメイン登場人物　犯人から逃げる　ホラーゲーム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>家の中を探索するホラーゲーム</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -559,7 +563,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="73.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -567,43 +571,43 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="91.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="91.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="73.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.45"/>
